--- a/delivery_order_templates/034_paypal_meal_kit_delivery_subscription_form--delivery_order_templates.xlsx
+++ b/delivery_order_templates/034_paypal_meal_kit_delivery_subscription_form--delivery_order_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>payment_details</t>
+          <t>payment_details_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Payment Details</t>
+          <t>Payment Details 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>meal_type</t>
+          <t>meal_type_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Meal Type</t>
+          <t>Meal Type 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>meal_plan</t>
+          <t>meal_plan_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Meal Plan</t>
+          <t>Meal Plan 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>subscription_start_date</t>
+          <t>subscription_start_date_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Subscription Start Date</t>
+          <t>Subscription Start Date 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1392,7 +1392,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>meal_type_choices</t>
+          <t>meal_type_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1409,7 +1409,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>meal_type_choices</t>
+          <t>meal_type_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>meal_type_choices</t>
+          <t>meal_type_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1443,51 +1443,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>meal_plan_choices</t>
+          <t>meal_plan_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>meal_plan_choices</t>
+          <t>meal_plan_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meal_plan_choices</t>
+          <t>meal_plan_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
